--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential US Bluechip Equity Fund.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential US Bluechip Equity Fund.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="202">
   <si>
     <t>ICICI Prudential Mutual Fund</t>
   </si>
@@ -22,7 +22,7 @@
     <t>ICICI Prudential US Bluechip Equity Fund</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -64,46 +64,469 @@
     <t>Foreign Securities/Overseas ETFs</t>
   </si>
   <si>
+    <t>Veeva Systems Inc</t>
+  </si>
+  <si>
+    <t>US9224751084</t>
+  </si>
+  <si>
+    <t>Health Care Technology</t>
+  </si>
+  <si>
+    <t>West Pharmaceutical Services Inc</t>
+  </si>
+  <si>
+    <t>US9553061055</t>
+  </si>
+  <si>
+    <t>Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>Huntington Ingalls Industries Inc</t>
+  </si>
+  <si>
+    <t>US4464131063</t>
+  </si>
+  <si>
+    <t>Aerospace &amp; Defense</t>
+  </si>
+  <si>
+    <t>Brown-Forman Corp</t>
+  </si>
+  <si>
+    <t>US1156372096</t>
+  </si>
+  <si>
+    <t>Beverages</t>
+  </si>
+  <si>
+    <t>Allegion plc</t>
+  </si>
+  <si>
+    <t>IE00BFRT3W74</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>Zimmer Biomet Holdings Inc</t>
+  </si>
+  <si>
+    <t>US98956P1021</t>
+  </si>
+  <si>
+    <t>Health Care Equipment</t>
+  </si>
+  <si>
+    <t>Microchip Technology Inc.</t>
+  </si>
+  <si>
+    <t>US5950171042</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Pfizer Inc</t>
+  </si>
+  <si>
+    <t>US7170811035</t>
+  </si>
+  <si>
+    <t>Monolithic Power Systems Inc</t>
+  </si>
+  <si>
+    <t>US6098391054</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>Corteva Inc</t>
+  </si>
+  <si>
+    <t>US22052L1044</t>
+  </si>
+  <si>
+    <t>Fertilizers &amp; Agricultural Chemicals</t>
+  </si>
+  <si>
+    <t>GE HealthCare Technologies Inc</t>
+  </si>
+  <si>
+    <t>US36266G1076</t>
+  </si>
+  <si>
+    <t>Campbell Soup Co</t>
+  </si>
+  <si>
+    <t>US1344291091</t>
+  </si>
+  <si>
+    <t>Packaged Foods &amp; Meats</t>
+  </si>
+  <si>
+    <t>US Bancorp Inc</t>
+  </si>
+  <si>
+    <t>US9029733048</t>
+  </si>
+  <si>
+    <t>Banks</t>
+  </si>
+  <si>
+    <t>Walt Disney</t>
+  </si>
+  <si>
+    <t>US2546871060</t>
+  </si>
+  <si>
+    <t>Media &amp; Entertainment</t>
+  </si>
+  <si>
+    <t>Boeing Co</t>
+  </si>
+  <si>
+    <t>US0970231058</t>
+  </si>
+  <si>
+    <t>MarketAxess Holdings Inc</t>
+  </si>
+  <si>
+    <t>US57060D1081</t>
+  </si>
+  <si>
+    <t>Capital Markets</t>
+  </si>
+  <si>
+    <t>Alphabet Inc</t>
+  </si>
+  <si>
+    <t>US02079K1079</t>
+  </si>
+  <si>
+    <t>Interactive Media &amp; Services</t>
+  </si>
+  <si>
+    <t>Nike Inc</t>
+  </si>
+  <si>
+    <t>US6541061031</t>
+  </si>
+  <si>
+    <t>Footwear</t>
+  </si>
+  <si>
+    <t>Adobe Inc</t>
+  </si>
+  <si>
+    <t>US00724F1012</t>
+  </si>
+  <si>
+    <t>Application Software</t>
+  </si>
+  <si>
+    <t>Agilent Technologies Co Ltd</t>
+  </si>
+  <si>
+    <t>US00846U1016</t>
+  </si>
+  <si>
+    <t>Estee Lauder Cos Inc</t>
+  </si>
+  <si>
+    <t>US5184391044</t>
+  </si>
+  <si>
+    <t>Consumer Durables</t>
+  </si>
+  <si>
+    <t>Danaher Corp</t>
+  </si>
+  <si>
+    <t>US2358511028</t>
+  </si>
+  <si>
+    <t>Trading</t>
+  </si>
+  <si>
+    <t>NXP Semiconductors NV</t>
+  </si>
+  <si>
+    <t>NL0009538784</t>
+  </si>
+  <si>
+    <t>International Flavors &amp; Fragrances Inc</t>
+  </si>
+  <si>
+    <t>US4595061015</t>
+  </si>
+  <si>
+    <t>Specialty Chemicals</t>
+  </si>
+  <si>
+    <t>TRANSUNION</t>
+  </si>
+  <si>
+    <t>US89400J1079</t>
+  </si>
+  <si>
+    <t>Household Appliances</t>
+  </si>
+  <si>
+    <t>Constellation Brands Inc</t>
+  </si>
+  <si>
+    <t>US21036P1084</t>
+  </si>
+  <si>
+    <t>Distillers &amp; Vintners</t>
+  </si>
+  <si>
+    <t>United Parcel Service Inc</t>
+  </si>
+  <si>
+    <t>US9113121068</t>
+  </si>
+  <si>
+    <t>Industrial Products</t>
+  </si>
+  <si>
+    <t>Bio-Rad Laboratories Inc</t>
+  </si>
+  <si>
+    <t>US0905722072</t>
+  </si>
+  <si>
+    <t>Biotechnology</t>
+  </si>
+  <si>
+    <t>Microsoft Corp</t>
+  </si>
+  <si>
+    <t>US5949181045</t>
+  </si>
+  <si>
+    <t>Systems Software</t>
+  </si>
+  <si>
+    <t>Mondelez International Inc</t>
+  </si>
+  <si>
+    <t>US6092071058</t>
+  </si>
+  <si>
+    <t>Amgen Inc</t>
+  </si>
+  <si>
+    <t>US0311621009</t>
+  </si>
+  <si>
+    <t>Charles Schwab Corp</t>
+  </si>
+  <si>
+    <t>US8085131055</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Synopsys Inc</t>
+  </si>
+  <si>
+    <t>US8716071076</t>
+  </si>
+  <si>
+    <t>Oracle Corp</t>
+  </si>
+  <si>
+    <t>US68389X1054</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Bristol-Myers Squibb Co</t>
+  </si>
+  <si>
+    <t>US1101221083</t>
+  </si>
+  <si>
+    <t>Thermo Fisher Scientific Inc</t>
+  </si>
+  <si>
+    <t>US8835561023</t>
+  </si>
+  <si>
+    <t>Healthcare Services</t>
+  </si>
+  <si>
+    <t>Amazon com</t>
+  </si>
+  <si>
+    <t>US0231351067</t>
+  </si>
+  <si>
+    <t>Internet &amp; Direct Marketing Retail</t>
+  </si>
+  <si>
+    <t>Merck &amp; Co Inc</t>
+  </si>
+  <si>
+    <t>US58933Y1055</t>
+  </si>
+  <si>
+    <t>Manhattan Associates Inc</t>
+  </si>
+  <si>
+    <t>US5627501092</t>
+  </si>
+  <si>
+    <t>Northrop Grumman Corp</t>
+  </si>
+  <si>
+    <t>US6668071029</t>
+  </si>
+  <si>
+    <t>Equifax Inc.</t>
+  </si>
+  <si>
+    <t>US2944291051</t>
+  </si>
+  <si>
+    <t>Research &amp; Consulting Services</t>
+  </si>
+  <si>
+    <t>Lam Research Corporation</t>
+  </si>
+  <si>
+    <t>US5128073062</t>
+  </si>
+  <si>
+    <t>Semiconductor Equipment</t>
+  </si>
+  <si>
     <t>Gilead Sciences Inc.</t>
   </si>
   <si>
     <t>US3755581036</t>
   </si>
   <si>
-    <t>Biotechnology</t>
-  </si>
-  <si>
-    <t>Corteva Inc</t>
-  </si>
-  <si>
-    <t>US22052L1044</t>
-  </si>
-  <si>
-    <t>Fertilizers &amp; Agricultural Chemicals</t>
-  </si>
-  <si>
-    <t>Walt Disney</t>
-  </si>
-  <si>
-    <t>US2546871060</t>
-  </si>
-  <si>
-    <t>Media &amp; Entertainment</t>
-  </si>
-  <si>
-    <t>Bristol-Myers Squibb Co</t>
-  </si>
-  <si>
-    <t>US1101221083</t>
-  </si>
-  <si>
-    <t>Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>Bio-Rad Laboratories Inc</t>
-  </si>
-  <si>
-    <t>US0905722072</t>
+    <t>Masco Corp.</t>
+  </si>
+  <si>
+    <t>US5745991068</t>
+  </si>
+  <si>
+    <t>Building Products</t>
+  </si>
+  <si>
+    <t>Applied Material (US)</t>
+  </si>
+  <si>
+    <t>US0382221051</t>
+  </si>
+  <si>
+    <t>Autodesk</t>
+  </si>
+  <si>
+    <t>US0527691069</t>
+  </si>
+  <si>
+    <t>Biogen Inc</t>
+  </si>
+  <si>
+    <t>US09062X1037</t>
+  </si>
+  <si>
+    <t>Cadence Design Systems Inc</t>
+  </si>
+  <si>
+    <t>US1273871087</t>
+  </si>
+  <si>
+    <t>Kenvue Inc</t>
+  </si>
+  <si>
+    <t>US49177J1025</t>
+  </si>
+  <si>
+    <t>Consumer Non Durables</t>
+  </si>
+  <si>
+    <t>TERADYNE INC</t>
+  </si>
+  <si>
+    <t>US8807701029</t>
+  </si>
+  <si>
+    <t>Comcast Corporation</t>
+  </si>
+  <si>
+    <t>US20030N1019</t>
+  </si>
+  <si>
+    <t>Cable &amp; Satellite</t>
+  </si>
+  <si>
+    <t>IDEX Corp</t>
+  </si>
+  <si>
+    <t>US45167R1041</t>
+  </si>
+  <si>
+    <t>Capital Goods</t>
+  </si>
+  <si>
+    <t>Salesforce.Com Inc</t>
+  </si>
+  <si>
+    <t>US79466L3024</t>
+  </si>
+  <si>
+    <t>Occidental Petroleum Corp</t>
+  </si>
+  <si>
+    <t>US6745991058</t>
+  </si>
+  <si>
+    <t>Oil &amp; Gas Exploration &amp; Production</t>
+  </si>
+  <si>
+    <t>Epam Systems Inc</t>
+  </si>
+  <si>
+    <t>US29414B1044</t>
+  </si>
+  <si>
+    <t>It - Services</t>
+  </si>
+  <si>
+    <t>Qualcomm Inc.</t>
+  </si>
+  <si>
+    <t>US7475251036</t>
+  </si>
+  <si>
+    <t>Freeport-McMoRan Inc</t>
+  </si>
+  <si>
+    <t>US35671D8570</t>
+  </si>
+  <si>
+    <t>Non - Ferrous Metals</t>
+  </si>
+  <si>
+    <t>Medtronic Plc</t>
+  </si>
+  <si>
+    <t>IE00BTN1Y115</t>
+  </si>
+  <si>
+    <t>ASML Holding NV-NY REG SHS</t>
+  </si>
+  <si>
+    <t>USN070592100</t>
   </si>
   <si>
     <t>Altria Group Inc</t>
@@ -115,454 +538,10 @@
     <t>Tobacco</t>
   </si>
   <si>
-    <t>Estee Lauder Cos Inc</t>
-  </si>
-  <si>
-    <t>US5184391044</t>
-  </si>
-  <si>
-    <t>Consumer Durables</t>
-  </si>
-  <si>
-    <t>Veeva Systems Inc</t>
-  </si>
-  <si>
-    <t>US9224751084</t>
-  </si>
-  <si>
-    <t>Health Care Technology</t>
-  </si>
-  <si>
-    <t>Agilent Technologies Co Ltd</t>
-  </si>
-  <si>
-    <t>US00846U1016</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>Boeing Co</t>
-  </si>
-  <si>
-    <t>US0970231058</t>
-  </si>
-  <si>
-    <t>Aerospace &amp; Defense</t>
-  </si>
-  <si>
-    <t>Zimmer Biomet Holdings Inc</t>
-  </si>
-  <si>
-    <t>US98956P1021</t>
-  </si>
-  <si>
-    <t>Health Care Equipment</t>
-  </si>
-  <si>
-    <t>US Bancorp Inc</t>
-  </si>
-  <si>
-    <t>US9029733048</t>
-  </si>
-  <si>
-    <t>Banks</t>
-  </si>
-  <si>
-    <t>Kenvue Inc</t>
-  </si>
-  <si>
-    <t>US49177J1025</t>
-  </si>
-  <si>
-    <t>Consumer Non Durables</t>
-  </si>
-  <si>
-    <t>Pfizer Inc</t>
-  </si>
-  <si>
-    <t>US7170811035</t>
-  </si>
-  <si>
-    <t>Campbell Soup Co</t>
-  </si>
-  <si>
-    <t>US1344291091</t>
-  </si>
-  <si>
-    <t>Packaged Foods &amp; Meats</t>
-  </si>
-  <si>
-    <t>Nike Inc</t>
-  </si>
-  <si>
-    <t>US6541061031</t>
-  </si>
-  <si>
-    <t>Footwear</t>
-  </si>
-  <si>
-    <t>International Flavors &amp; Fragrances Inc</t>
-  </si>
-  <si>
-    <t>US4595061015</t>
-  </si>
-  <si>
-    <t>Specialty Chemicals</t>
-  </si>
-  <si>
-    <t>MarketAxess Holdings Inc</t>
-  </si>
-  <si>
-    <t>US57060D1081</t>
-  </si>
-  <si>
-    <t>Capital Markets</t>
-  </si>
-  <si>
-    <t>ETSY INC</t>
-  </si>
-  <si>
-    <t>US29786A1060</t>
-  </si>
-  <si>
-    <t>Internet &amp; Direct Marketing Retail</t>
-  </si>
-  <si>
-    <t>TRANSUNION</t>
-  </si>
-  <si>
-    <t>US89400J1079</t>
-  </si>
-  <si>
-    <t>Household Appliances</t>
-  </si>
-  <si>
-    <t>Adobe Inc</t>
-  </si>
-  <si>
-    <t>US00724F1012</t>
-  </si>
-  <si>
-    <t>Application Software</t>
-  </si>
-  <si>
-    <t>Alphabet Inc</t>
-  </si>
-  <si>
-    <t>US02079K1079</t>
-  </si>
-  <si>
-    <t>Interactive Media &amp; Services</t>
-  </si>
-  <si>
-    <t>Brown-Forman Corp</t>
-  </si>
-  <si>
-    <t>US1156372096</t>
-  </si>
-  <si>
-    <t>Beverages</t>
-  </si>
-  <si>
-    <t>Allegion plc</t>
-  </si>
-  <si>
-    <t>IE00BFRT3W74</t>
-  </si>
-  <si>
-    <t>Construction</t>
-  </si>
-  <si>
-    <t>NXP Semiconductors NV</t>
-  </si>
-  <si>
-    <t>NL0009538784</t>
-  </si>
-  <si>
-    <t>Semiconductors</t>
-  </si>
-  <si>
-    <t>Medtronic Plc</t>
-  </si>
-  <si>
-    <t>IE00BTN1Y115</t>
-  </si>
-  <si>
-    <t>United Parcel Service Inc</t>
-  </si>
-  <si>
-    <t>US9113121068</t>
-  </si>
-  <si>
-    <t>Industrial Products</t>
-  </si>
-  <si>
-    <t>Microchip Technology Inc.</t>
-  </si>
-  <si>
-    <t>US5950171042</t>
-  </si>
-  <si>
-    <t>Huntington Ingalls Industries Inc</t>
-  </si>
-  <si>
-    <t>US4464131063</t>
-  </si>
-  <si>
-    <t>Charles Schwab Corp</t>
-  </si>
-  <si>
-    <t>US8085131055</t>
-  </si>
-  <si>
-    <t>Finance</t>
-  </si>
-  <si>
-    <t>Comcast Corporation</t>
-  </si>
-  <si>
-    <t>US20030N1019</t>
-  </si>
-  <si>
-    <t>Cable &amp; Satellite</t>
-  </si>
-  <si>
-    <t>Amazon com</t>
-  </si>
-  <si>
-    <t>US0231351067</t>
-  </si>
-  <si>
-    <t>Equifax Inc.</t>
-  </si>
-  <si>
-    <t>US2944291051</t>
-  </si>
-  <si>
-    <t>Research &amp; Consulting Services</t>
-  </si>
-  <si>
-    <t>Autodesk</t>
-  </si>
-  <si>
-    <t>US0527691069</t>
-  </si>
-  <si>
-    <t>Honeywell Internation India Pvt Ltd</t>
-  </si>
-  <si>
-    <t>US4385161066</t>
-  </si>
-  <si>
-    <t>Industrial Conglomerates</t>
-  </si>
-  <si>
-    <t>Amgen Inc</t>
-  </si>
-  <si>
-    <t>US0311621009</t>
-  </si>
-  <si>
-    <t>West Pharmaceutical Services Inc</t>
-  </si>
-  <si>
-    <t>US9553061055</t>
-  </si>
-  <si>
-    <t>Thermo Fisher Scientific Inc</t>
-  </si>
-  <si>
-    <t>US8835561023</t>
-  </si>
-  <si>
-    <t>Healthcare Services</t>
-  </si>
-  <si>
-    <t>Microsoft Corp</t>
-  </si>
-  <si>
-    <t>US5949181045</t>
-  </si>
-  <si>
-    <t>Systems Software</t>
-  </si>
-  <si>
-    <t>Northrop Grumman Corp</t>
-  </si>
-  <si>
-    <t>US6668071029</t>
-  </si>
-  <si>
-    <t>Danaher Corp</t>
-  </si>
-  <si>
-    <t>US2358511028</t>
-  </si>
-  <si>
-    <t>Trading</t>
-  </si>
-  <si>
-    <t>Emerson Electric</t>
-  </si>
-  <si>
-    <t>US2910111044</t>
-  </si>
-  <si>
-    <t>Electrical Components &amp; Equipment</t>
-  </si>
-  <si>
-    <t>Lam Research Corporation</t>
-  </si>
-  <si>
-    <t>US5128073062</t>
-  </si>
-  <si>
-    <t>Semiconductor Equipment</t>
-  </si>
-  <si>
-    <t>Mondelez International Inc</t>
-  </si>
-  <si>
-    <t>US6092071058</t>
-  </si>
-  <si>
-    <t>Merck &amp; Co Inc</t>
-  </si>
-  <si>
-    <t>US58933Y1055</t>
-  </si>
-  <si>
-    <t>Salesforce.Com Inc</t>
-  </si>
-  <si>
-    <t>US79466L3024</t>
-  </si>
-  <si>
-    <t>Biogen Inc</t>
-  </si>
-  <si>
-    <t>US09062X1037</t>
-  </si>
-  <si>
-    <t>TERADYNE INC</t>
-  </si>
-  <si>
-    <t>US8807701029</t>
-  </si>
-  <si>
-    <t>Constellation Brands Inc</t>
-  </si>
-  <si>
-    <t>US21036P1084</t>
-  </si>
-  <si>
-    <t>Distillers &amp; Vintners</t>
-  </si>
-  <si>
-    <t>Masco Corp.</t>
-  </si>
-  <si>
-    <t>US5745991068</t>
-  </si>
-  <si>
-    <t>Building Products</t>
-  </si>
-  <si>
-    <t>Monolithic Power Systems Inc</t>
-  </si>
-  <si>
-    <t>US6098391054</t>
-  </si>
-  <si>
-    <t>Epam Systems Inc</t>
-  </si>
-  <si>
-    <t>US29414B1044</t>
-  </si>
-  <si>
-    <t>It - Services</t>
-  </si>
-  <si>
-    <t>IDEX Corp</t>
-  </si>
-  <si>
-    <t>US45167R1041</t>
-  </si>
-  <si>
-    <t>Capital Goods</t>
-  </si>
-  <si>
-    <t>Occidental Petroleum Corp</t>
-  </si>
-  <si>
-    <t>US6745991058</t>
-  </si>
-  <si>
-    <t>Oil &amp; Gas Exploration &amp; Production</t>
-  </si>
-  <si>
-    <t>OTIS WORLDWIDE CORP</t>
-  </si>
-  <si>
-    <t>US68902V1070</t>
-  </si>
-  <si>
-    <t>Industrial Capital Goods</t>
-  </si>
-  <si>
-    <t>Cognizant Tech Solutions</t>
-  </si>
-  <si>
-    <t>US1924461023</t>
-  </si>
-  <si>
-    <t>It Consulting &amp; Other Services</t>
-  </si>
-  <si>
-    <t>Freeport-McMoRan Inc</t>
-  </si>
-  <si>
-    <t>US35671D8570</t>
-  </si>
-  <si>
-    <t>Non - Ferrous Metals</t>
-  </si>
-  <si>
-    <t>Newmont Corp</t>
-  </si>
-  <si>
-    <t>US6516391066</t>
-  </si>
-  <si>
-    <t>Minerals/Mining</t>
-  </si>
-  <si>
-    <t>Globant SA</t>
-  </si>
-  <si>
-    <t>LU0974299876</t>
-  </si>
-  <si>
-    <t>Software</t>
-  </si>
-  <si>
-    <t>ASML Holding NV-NY REG SHS</t>
-  </si>
-  <si>
-    <t>USN070592100</t>
-  </si>
-  <si>
-    <t>Qualcomm Inc.</t>
-  </si>
-  <si>
-    <t>US7475251036</t>
-  </si>
-  <si>
-    <t>The Clorox Company</t>
-  </si>
-  <si>
-    <t>US1890541097</t>
+    <t>Yum China Holdings Inc.</t>
+  </si>
+  <si>
+    <t>US98850P1093</t>
   </si>
   <si>
     <t>Unlisted</t>
@@ -628,7 +607,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -1032,13 +1011,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>123</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>134</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1056,7 +1035,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="24079200"/>
+          <a:off x="666750" y="23888700"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1071,13 +1050,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>139</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>149</xdr:row>
+      <xdr:row>148</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1095,7 +1074,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="666750" y="26936700"/>
+          <a:off x="666750" y="26746200"/>
           <a:ext cx="3571875" cy="1905000"/>
         </a:xfrm>
         <a:prstGeom prst="rect"/>
@@ -1429,14 +1408,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="B1:J138"/>
+  <dimension ref="B1:J137"/>
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="21" width="10.0" collapsed="true"/>
     <col min="2" max="2" bestFit="true" customWidth="true" style="21" width="53.57142857142857" collapsed="true"/>
     <col min="3" max="3" bestFit="true" customWidth="true" style="21" width="16.857142857142858" collapsed="true"/>
     <col min="4" max="4" bestFit="true" customWidth="true" style="21" width="9.714285714285714" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="36.857142857142854" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="21" width="36.0" collapsed="true"/>
     <col min="6" max="6" bestFit="true" customWidth="true" style="21" width="10.857142857142858" collapsed="true"/>
     <col min="7" max="7" bestFit="true" customWidth="true" style="21" width="38.714285714285715" collapsed="true"/>
     <col min="8" max="8" bestFit="true" customWidth="true" style="21" width="11.714285714285714" collapsed="true"/>
@@ -1529,10 +1508,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="9">
-        <v>328497.2299999999</v>
+        <v>295552.30999999994</v>
       </c>
       <c r="H5" s="10">
-        <v>0.9856487162785</v>
+        <v>0.9801208115625998</v>
       </c>
       <c r="I5" s="9" t="s">
         <v>13</v>
@@ -1566,10 +1545,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="9">
-        <v>328497.2299999999</v>
+        <v>295552.30999999994</v>
       </c>
       <c r="H7" s="10">
-        <v>0.9856487162785</v>
+        <v>0.9801208115625998</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>13</v>
@@ -1603,10 +1582,10 @@
         <v>13</v>
       </c>
       <c r="G9" s="9">
-        <v>328497.2299999999</v>
+        <v>295552.30999999994</v>
       </c>
       <c r="H9" s="10">
-        <v>0.9856487162785</v>
+        <v>0.9801208115625998</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>13</v>
@@ -1629,13 +1608,13 @@
         <v>18</v>
       </c>
       <c r="F10" s="14">
-        <v>113725</v>
+        <v>38291</v>
       </c>
       <c r="G10" s="15">
-        <v>9577.40</v>
+        <v>9154.67</v>
       </c>
       <c r="H10" s="16">
-        <v>0.0287367781314</v>
+        <v>0.0303590338712</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>13</v>
@@ -1658,13 +1637,13 @@
         <v>21</v>
       </c>
       <c r="F11" s="14">
-        <v>164840</v>
+        <v>47000</v>
       </c>
       <c r="G11" s="15">
-        <v>9321.84</v>
+        <v>8470.81</v>
       </c>
       <c r="H11" s="16">
-        <v>0.0279699759702</v>
+        <v>0.0280911936429</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>13</v>
@@ -1687,13 +1666,13 @@
         <v>24</v>
       </c>
       <c r="F12" s="14">
-        <v>92938</v>
+        <v>42405</v>
       </c>
       <c r="G12" s="15">
-        <v>9103.91</v>
+        <v>8085.22</v>
       </c>
       <c r="H12" s="16">
-        <v>0.0273160817966</v>
+        <v>0.0268124867238</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>13</v>
@@ -1716,13 +1695,13 @@
         <v>27</v>
       </c>
       <c r="F13" s="14">
-        <v>174712</v>
+        <v>281600</v>
       </c>
       <c r="G13" s="15">
-        <v>8923.43</v>
+        <v>8025.12</v>
       </c>
       <c r="H13" s="16">
-        <v>0.0267745555246</v>
+        <v>0.0266131810213</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>13</v>
@@ -1742,16 +1721,16 @@
         <v>13</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F14" s="14">
-        <v>28316</v>
+        <v>60986</v>
       </c>
       <c r="G14" s="15">
-        <v>8853.61</v>
+        <v>7438.88</v>
       </c>
       <c r="H14" s="16">
-        <v>0.0265650621496</v>
+        <v>0.0246690716196</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>13</v>
@@ -1762,25 +1741,25 @@
     </row>
     <row r="15" spans="2:10" ht="15" customHeight="1">
       <c r="B15" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F15" s="14">
-        <v>193878</v>
+        <v>93999</v>
       </c>
       <c r="G15" s="15">
-        <v>8773.52</v>
+        <v>7405.70</v>
       </c>
       <c r="H15" s="16">
-        <v>0.0263247538655</v>
+        <v>0.0245590389539</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>13</v>
@@ -1791,25 +1770,25 @@
     </row>
     <row r="16" spans="2:10" ht="15" customHeight="1">
       <c r="B16" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16" s="14">
-        <v>115367</v>
+        <v>148020</v>
       </c>
       <c r="G16" s="15">
-        <v>8339.29</v>
+        <v>7343.47</v>
       </c>
       <c r="H16" s="16">
-        <v>0.0250218562975</v>
+        <v>0.0243526696715</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>13</v>
@@ -1820,25 +1799,25 @@
     </row>
     <row r="17" spans="2:10" ht="15" customHeight="1">
       <c r="B17" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>40982</v>
+        <v>362963</v>
       </c>
       <c r="G17" s="15">
-        <v>8282.45</v>
+        <v>7287.84</v>
       </c>
       <c r="H17" s="16">
-        <v>0.0248513091272</v>
+        <v>0.0241681875379</v>
       </c>
       <c r="I17" s="15" t="s">
         <v>13</v>
@@ -1861,13 +1840,13 @@
         <v>41</v>
       </c>
       <c r="F18" s="14">
-        <v>62528</v>
+        <v>12877</v>
       </c>
       <c r="G18" s="15">
-        <v>8208.62</v>
+        <v>7285.52</v>
       </c>
       <c r="H18" s="16">
-        <v>0.0246297838354</v>
+        <v>0.0241604938735</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>13</v>
@@ -1890,13 +1869,13 @@
         <v>44</v>
       </c>
       <c r="F19" s="14">
-        <v>53582</v>
+        <v>119840</v>
       </c>
       <c r="G19" s="15">
-        <v>8194.8</v>
+        <v>7252.51</v>
       </c>
       <c r="H19" s="16">
-        <v>0.0245883172292</v>
+        <v>0.0240510249677</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>13</v>
@@ -1916,16 +1895,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="F20" s="14">
-        <v>84999</v>
+        <v>120200</v>
       </c>
       <c r="G20" s="15">
-        <v>8062.58</v>
+        <v>7247.58</v>
       </c>
       <c r="H20" s="16">
-        <v>0.0241915940262</v>
+        <v>0.0240346759309</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>13</v>
@@ -1936,25 +1915,25 @@
     </row>
     <row r="21" spans="2:10" ht="15" customHeight="1">
       <c r="B21" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="D21" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>50</v>
-      </c>
       <c r="F21" s="14">
-        <v>194027</v>
+        <v>249045</v>
       </c>
       <c r="G21" s="15">
-        <v>8032.19</v>
+        <v>7246.37</v>
       </c>
       <c r="H21" s="16">
-        <v>0.0241004094994</v>
+        <v>0.0240306632869</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>13</v>
@@ -1965,25 +1944,25 @@
     </row>
     <row r="22" spans="2:10" ht="15" customHeight="1">
       <c r="B22" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="D22" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>53</v>
-      </c>
       <c r="F22" s="14">
-        <v>423060</v>
+        <v>194027</v>
       </c>
       <c r="G22" s="15">
-        <v>7803.75</v>
+        <v>7229.40</v>
       </c>
       <c r="H22" s="16">
-        <v>0.0234149803018</v>
+        <v>0.0239743867849</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>13</v>
@@ -1994,25 +1973,25 @@
     </row>
     <row r="23" spans="2:10" ht="15" customHeight="1">
       <c r="B23" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>27</v>
-      </c>
       <c r="F23" s="14">
-        <v>337963</v>
+        <v>73573</v>
       </c>
       <c r="G23" s="15">
-        <v>7765.48</v>
+        <v>7108.93</v>
       </c>
       <c r="H23" s="16">
-        <v>0.0233001520083</v>
+        <v>0.0235748799965</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>13</v>
@@ -2032,16 +2011,16 @@
         <v>13</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="F24" s="14">
-        <v>230045</v>
+        <v>40082</v>
       </c>
       <c r="G24" s="15">
-        <v>7727.41</v>
+        <v>7103.03</v>
       </c>
       <c r="H24" s="16">
-        <v>0.0231859238103</v>
+        <v>0.0235553142121</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>13</v>
@@ -2052,25 +2031,25 @@
     </row>
     <row r="25" spans="2:10" ht="15" customHeight="1">
       <c r="B25" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="D25" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>61</v>
-      </c>
       <c r="F25" s="14">
-        <v>111580</v>
+        <v>37889</v>
       </c>
       <c r="G25" s="15">
-        <v>7434.27</v>
+        <v>7008.80</v>
       </c>
       <c r="H25" s="16">
-        <v>0.0223063636852</v>
+        <v>0.0232428254209</v>
       </c>
       <c r="I25" s="15" t="s">
         <v>13</v>
@@ -2081,25 +2060,25 @@
     </row>
     <row r="26" spans="2:10" ht="15" customHeight="1">
       <c r="B26" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="D26" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>64</v>
-      </c>
       <c r="F26" s="14">
-        <v>96486</v>
+        <v>45978</v>
       </c>
       <c r="G26" s="15">
-        <v>7280.45</v>
+        <v>6793.17</v>
       </c>
       <c r="H26" s="16">
-        <v>0.0218448301571</v>
+        <v>0.0225277457432</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>13</v>
@@ -2110,25 +2089,25 @@
     </row>
     <row r="27" spans="2:10" ht="15" customHeight="1">
       <c r="B27" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="D27" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>67</v>
-      </c>
       <c r="F27" s="14">
-        <v>37889</v>
+        <v>129580</v>
       </c>
       <c r="G27" s="15">
-        <v>7242.74</v>
+        <v>6711.08</v>
       </c>
       <c r="H27" s="16">
-        <v>0.0217316821312</v>
+        <v>0.0222555160407</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>13</v>
@@ -2139,25 +2118,25 @@
     </row>
     <row r="28" spans="2:10" ht="15" customHeight="1">
       <c r="B28" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="D28" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>70</v>
-      </c>
       <c r="F28" s="14">
-        <v>151760</v>
+        <v>18748</v>
       </c>
       <c r="G28" s="15">
-        <v>7219.95</v>
+        <v>6651.97</v>
       </c>
       <c r="H28" s="16">
-        <v>0.0216633012373</v>
+        <v>0.0220594934105</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>13</v>
@@ -2168,25 +2147,25 @@
     </row>
     <row r="29" spans="2:10" ht="15" customHeight="1">
       <c r="B29" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C29" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>72</v>
-      </c>
       <c r="D29" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="F29" s="14">
-        <v>83791</v>
+        <v>69528</v>
       </c>
       <c r="G29" s="15">
-        <v>7205.32</v>
+        <v>6651.52</v>
       </c>
       <c r="H29" s="16">
-        <v>0.0216194042439</v>
+        <v>0.0220580011049</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>13</v>
@@ -2197,25 +2176,25 @@
     </row>
     <row r="30" spans="2:10" ht="15" customHeight="1">
       <c r="B30" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>76</v>
-      </c>
       <c r="F30" s="14">
-        <v>18748</v>
+        <v>115367</v>
       </c>
       <c r="G30" s="15">
-        <v>7105.73</v>
+        <v>6601.17</v>
       </c>
       <c r="H30" s="16">
-        <v>0.0213205866385</v>
+        <v>0.0218910286902</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>13</v>
@@ -2226,25 +2205,25 @@
     </row>
     <row r="31" spans="2:10" ht="15" customHeight="1">
       <c r="B31" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>79</v>
-      </c>
       <c r="F31" s="14">
-        <v>39678</v>
+        <v>40000</v>
       </c>
       <c r="G31" s="15">
-        <v>7068.03</v>
+        <v>6492.89</v>
       </c>
       <c r="H31" s="16">
-        <v>0.0212074686174</v>
+        <v>0.0215319468022</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>13</v>
@@ -2255,25 +2234,25 @@
     </row>
     <row r="32" spans="2:10" ht="15" customHeight="1">
       <c r="B32" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D32" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="F32" s="14">
-        <v>246600</v>
+        <v>38800</v>
       </c>
       <c r="G32" s="15">
-        <v>7052.84</v>
+        <v>6338.90</v>
       </c>
       <c r="H32" s="16">
-        <v>0.0211618913563</v>
+        <v>0.0210212798283</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>13</v>
@@ -2284,25 +2263,25 @@
     </row>
     <row r="33" spans="2:10" ht="15" customHeight="1">
       <c r="B33" s="12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F33" s="14">
-        <v>60986</v>
+        <v>96486</v>
       </c>
       <c r="G33" s="15">
-        <v>7013.34</v>
+        <v>6314.22</v>
       </c>
       <c r="H33" s="16">
-        <v>0.0210433724748</v>
+        <v>0.0209394351571</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>13</v>
@@ -2313,25 +2292,25 @@
     </row>
     <row r="34" spans="2:10" ht="15" customHeight="1">
       <c r="B34" s="12" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D34" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F34" s="14">
-        <v>38800</v>
+        <v>83791</v>
       </c>
       <c r="G34" s="15">
-        <v>7010.80</v>
+        <v>6133.05</v>
       </c>
       <c r="H34" s="16">
-        <v>0.0210357512606</v>
+        <v>0.0203386329254</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>13</v>
@@ -2342,25 +2321,25 @@
     </row>
     <row r="35" spans="2:10" ht="15" customHeight="1">
       <c r="B35" s="12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D35" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="F35" s="14">
-        <v>81546</v>
+        <v>40100</v>
       </c>
       <c r="G35" s="15">
-        <v>6416.67</v>
+        <v>6111.17</v>
       </c>
       <c r="H35" s="16">
-        <v>0.0192530772582</v>
+        <v>0.0202660737113</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>13</v>
@@ -2371,25 +2350,25 @@
     </row>
     <row r="36" spans="2:10" ht="15" customHeight="1">
       <c r="B36" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>93</v>
-      </c>
       <c r="F36" s="14">
-        <v>64600</v>
+        <v>72600</v>
       </c>
       <c r="G36" s="15">
-        <v>6393.49</v>
+        <v>6053.03</v>
       </c>
       <c r="H36" s="16">
-        <v>0.0191835261778</v>
+        <v>0.0200732678287</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>13</v>
@@ -2400,25 +2379,25 @@
     </row>
     <row r="37" spans="2:10" ht="15" customHeight="1">
       <c r="B37" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>88</v>
-      </c>
       <c r="F37" s="14">
-        <v>131020</v>
+        <v>28316</v>
       </c>
       <c r="G37" s="15">
-        <v>6164</v>
+        <v>5492.59</v>
       </c>
       <c r="H37" s="16">
-        <v>0.0184949464784</v>
+        <v>0.018214717281</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>13</v>
@@ -2429,25 +2408,25 @@
     </row>
     <row r="38" spans="2:10" ht="15" customHeight="1">
       <c r="B38" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C38" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="D38" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="D38" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" s="13" t="s">
-        <v>44</v>
-      </c>
       <c r="F38" s="14">
-        <v>35584</v>
+        <v>11097</v>
       </c>
       <c r="G38" s="15">
-        <v>6081.62</v>
+        <v>4366.73</v>
       </c>
       <c r="H38" s="16">
-        <v>0.0182477670996</v>
+        <v>0.0144811013369</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>13</v>
@@ -2467,16 +2446,16 @@
         <v>13</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="F39" s="14">
-        <v>81080</v>
+        <v>75000</v>
       </c>
       <c r="G39" s="15">
-        <v>5810.98</v>
+        <v>4326.67</v>
       </c>
       <c r="H39" s="16">
-        <v>0.0174357177299</v>
+        <v>0.0143482529768</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>13</v>
@@ -2487,25 +2466,25 @@
     </row>
     <row r="40" spans="2:10" ht="15" customHeight="1">
       <c r="B40" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>102</v>
-      </c>
       <c r="D40" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="F40" s="14">
-        <v>192818</v>
+        <v>17000</v>
       </c>
       <c r="G40" s="15">
-        <v>5623.25</v>
+        <v>4187.61</v>
       </c>
       <c r="H40" s="16">
-        <v>0.0168724379923</v>
+        <v>0.0138870973863</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>13</v>
@@ -2516,25 +2495,25 @@
     </row>
     <row r="41" spans="2:10" ht="15" customHeight="1">
       <c r="B41" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>70</v>
-      </c>
       <c r="F41" s="14">
-        <v>26550</v>
+        <v>55080</v>
       </c>
       <c r="G41" s="15">
-        <v>5467.42</v>
+        <v>4159.15</v>
       </c>
       <c r="H41" s="16">
-        <v>0.0164048735034</v>
+        <v>0.0137927173481</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>13</v>
@@ -2545,25 +2524,25 @@
     </row>
     <row r="42" spans="2:10" ht="15" customHeight="1">
       <c r="B42" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>107</v>
-      </c>
       <c r="D42" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="F42" s="14">
-        <v>19791</v>
+        <v>10400</v>
       </c>
       <c r="G42" s="15">
-        <v>4711.71</v>
+        <v>4124.64</v>
       </c>
       <c r="H42" s="16">
-        <v>0.0141373822634</v>
+        <v>0.0136782740903</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>13</v>
@@ -2574,25 +2553,25 @@
     </row>
     <row r="43" spans="2:10" ht="15" customHeight="1">
       <c r="B43" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E43" s="13" t="s">
-        <v>76</v>
-      </c>
       <c r="F43" s="14">
-        <v>16574</v>
+        <v>28633</v>
       </c>
       <c r="G43" s="15">
-        <v>4470.83</v>
+        <v>4051.32</v>
       </c>
       <c r="H43" s="16">
-        <v>0.0134146271194</v>
+        <v>0.0134351277657</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>13</v>
@@ -2603,25 +2582,25 @@
     </row>
     <row r="44" spans="2:10" ht="15" customHeight="1">
       <c r="B44" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C44" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>112</v>
-      </c>
       <c r="D44" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="F44" s="14">
-        <v>22575</v>
+        <v>97849</v>
       </c>
       <c r="G44" s="15">
-        <v>4375.81</v>
+        <v>4038.10</v>
       </c>
       <c r="H44" s="16">
-        <v>0.0131295216985</v>
+        <v>0.0133912871436</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>13</v>
@@ -2632,25 +2611,25 @@
     </row>
     <row r="45" spans="2:10" ht="15" customHeight="1">
       <c r="B45" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D45" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>18</v>
-      </c>
       <c r="F45" s="14">
-        <v>17000</v>
+        <v>11720</v>
       </c>
       <c r="G45" s="15">
-        <v>4203.96</v>
+        <v>4035.45</v>
       </c>
       <c r="H45" s="16">
-        <v>0.0126138895518</v>
+        <v>0.0133824991218</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>13</v>
@@ -2661,25 +2640,25 @@
     </row>
     <row r="46" spans="2:10" ht="15" customHeight="1">
       <c r="B46" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="D46" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="D46" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E46" s="13" t="s">
-        <v>27</v>
-      </c>
       <c r="F46" s="14">
-        <v>14000</v>
+        <v>22800</v>
       </c>
       <c r="G46" s="15">
-        <v>4142.93</v>
+        <v>3995.43</v>
       </c>
       <c r="H46" s="16">
-        <v>0.0124307703786</v>
+        <v>0.0132497834111</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>13</v>
@@ -2699,16 +2678,16 @@
         <v>13</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="F47" s="14">
-        <v>7920</v>
+        <v>60800</v>
       </c>
       <c r="G47" s="15">
-        <v>4101.76</v>
+        <v>3993.41</v>
       </c>
       <c r="H47" s="16">
-        <v>0.0123072406987</v>
+        <v>0.0132430846171</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>13</v>
@@ -2719,25 +2698,25 @@
     </row>
     <row r="48" spans="2:10" ht="15" customHeight="1">
       <c r="B48" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C48" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="C48" s="13" t="s">
-        <v>122</v>
-      </c>
       <c r="D48" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>123</v>
+        <v>69</v>
       </c>
       <c r="F48" s="14">
-        <v>11097</v>
+        <v>24226</v>
       </c>
       <c r="G48" s="15">
-        <v>3990.63</v>
+        <v>3909.23</v>
       </c>
       <c r="H48" s="16">
-        <v>0.011973797577</v>
+        <v>0.0129639239842</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>13</v>
@@ -2748,25 +2727,25 @@
     </row>
     <row r="49" spans="2:10" ht="15" customHeight="1">
       <c r="B49" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C49" s="13" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D49" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="F49" s="14">
         <v>9260</v>
       </c>
       <c r="G49" s="15">
-        <v>3909.36</v>
+        <v>3837.07</v>
       </c>
       <c r="H49" s="16">
-        <v>0.0117299487288</v>
+        <v>0.0127246244917</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>13</v>
@@ -2777,25 +2756,25 @@
     </row>
     <row r="50" spans="2:10" ht="15" customHeight="1">
       <c r="B50" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="C50" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="13" t="s">
-        <v>128</v>
-      </c>
       <c r="F50" s="14">
-        <v>20000</v>
+        <v>16791</v>
       </c>
       <c r="G50" s="15">
-        <v>3859.70</v>
+        <v>3791.81</v>
       </c>
       <c r="H50" s="16">
-        <v>0.0115809449907</v>
+        <v>0.0125745317115</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>13</v>
@@ -2806,25 +2785,25 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1">
       <c r="B51" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C51" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="13" t="s">
-        <v>131</v>
-      </c>
       <c r="F51" s="14">
-        <v>33956</v>
+        <v>53720</v>
       </c>
       <c r="G51" s="15">
-        <v>3823.12</v>
+        <v>3709.77</v>
       </c>
       <c r="H51" s="16">
-        <v>0.0114711875049</v>
+        <v>0.0123024678207</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>13</v>
@@ -2835,25 +2814,25 @@
     </row>
     <row r="52" spans="2:10" ht="15" customHeight="1">
       <c r="B52" s="12" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D52" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="F52" s="14">
-        <v>53720</v>
+        <v>36925</v>
       </c>
       <c r="G52" s="15">
-        <v>3772.37</v>
+        <v>3474.42</v>
       </c>
       <c r="H52" s="16">
-        <v>0.0113189132457</v>
+        <v>0.0115219919956</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>13</v>
@@ -2864,25 +2843,25 @@
     </row>
     <row r="53" spans="2:10" ht="15" customHeight="1">
       <c r="B53" s="12" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D53" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="F53" s="14">
-        <v>75000</v>
+        <v>60464</v>
       </c>
       <c r="G53" s="15">
-        <v>3768.25</v>
+        <v>3226.07</v>
       </c>
       <c r="H53" s="16">
-        <v>0.0113065512763</v>
+        <v>0.0106984051201</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>13</v>
@@ -2893,25 +2872,25 @@
     </row>
     <row r="54" spans="2:10" ht="15" customHeight="1">
       <c r="B54" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D54" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E54" s="13" t="s">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="F54" s="14">
-        <v>43000</v>
+        <v>24000</v>
       </c>
       <c r="G54" s="15">
-        <v>3681.62</v>
+        <v>3215.67</v>
       </c>
       <c r="H54" s="16">
-        <v>0.0110466198659</v>
+        <v>0.0106639162797</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>13</v>
@@ -2922,25 +2901,25 @@
     </row>
     <row r="55" spans="2:10" ht="15" customHeight="1">
       <c r="B55" s="12" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D55" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F55" s="14">
-        <v>11145</v>
+        <v>12574</v>
       </c>
       <c r="G55" s="15">
-        <v>3299.52</v>
+        <v>3182.69</v>
       </c>
       <c r="H55" s="16">
-        <v>0.0099001372168</v>
+        <v>0.0105545468609</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>13</v>
@@ -2951,25 +2930,25 @@
     </row>
     <row r="56" spans="2:10" ht="15" customHeight="1">
       <c r="B56" s="12" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D56" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>18</v>
+        <v>94</v>
       </c>
       <c r="F56" s="14">
         <v>26352</v>
       </c>
       <c r="G56" s="15">
-        <v>3286.17</v>
+        <v>2923.53</v>
       </c>
       <c r="H56" s="16">
-        <v>0.0098600808353</v>
+        <v>0.0096951114888</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>13</v>
@@ -2980,25 +2959,25 @@
     </row>
     <row r="57" spans="2:10" ht="15" customHeight="1">
       <c r="B57" s="12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D57" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
       <c r="F57" s="14">
-        <v>31717</v>
+        <v>11596</v>
       </c>
       <c r="G57" s="15">
-        <v>3181.92</v>
+        <v>2845.44</v>
       </c>
       <c r="H57" s="16">
-        <v>0.0095472810023</v>
+        <v>0.0094361467249</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>13</v>
@@ -3009,25 +2988,25 @@
     </row>
     <row r="58" spans="2:10" ht="15" customHeight="1">
       <c r="B58" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C58" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="D58" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>147</v>
-      </c>
       <c r="F58" s="14">
-        <v>20000</v>
+        <v>130060</v>
       </c>
       <c r="G58" s="15">
-        <v>3132.95</v>
+        <v>2653.69</v>
       </c>
       <c r="H58" s="16">
-        <v>0.009400347594</v>
+        <v>0.0088002587306</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>13</v>
@@ -3038,25 +3017,25 @@
     </row>
     <row r="59" spans="2:10" ht="15" customHeight="1">
       <c r="B59" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D59" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E59" s="13" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="F59" s="14">
-        <v>45464</v>
+        <v>38717</v>
       </c>
       <c r="G59" s="15">
-        <v>3122.89</v>
+        <v>2601.22</v>
       </c>
       <c r="H59" s="16">
-        <v>0.0093701627851</v>
+        <v>0.0086262558985</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>13</v>
@@ -3067,25 +3046,25 @@
     </row>
     <row r="60" spans="2:10" ht="15" customHeight="1">
       <c r="B60" s="12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C60" s="13" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D60" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>41</v>
+        <v>150</v>
       </c>
       <c r="F60" s="14">
-        <v>5377</v>
+        <v>87818</v>
       </c>
       <c r="G60" s="15">
-        <v>2969.32</v>
+        <v>2594.99</v>
       </c>
       <c r="H60" s="16">
-        <v>0.0089093793765</v>
+        <v>0.0086055957566</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>13</v>
@@ -3096,25 +3075,25 @@
     </row>
     <row r="61" spans="2:10" ht="15" customHeight="1">
       <c r="B61" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="C61" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C61" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="D61" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="13" t="s">
-        <v>155</v>
-      </c>
       <c r="F61" s="14">
-        <v>9450</v>
+        <v>15341</v>
       </c>
       <c r="G61" s="15">
-        <v>2079.33</v>
+        <v>2372.3</v>
       </c>
       <c r="H61" s="16">
-        <v>0.0062389839488</v>
+        <v>0.0078671034622</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>13</v>
@@ -3125,25 +3104,25 @@
     </row>
     <row r="62" spans="2:10" ht="15" customHeight="1">
       <c r="B62" s="12" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D62" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E62" s="13" t="s">
-        <v>158</v>
+        <v>69</v>
       </c>
       <c r="F62" s="14">
-        <v>10341</v>
+        <v>9445</v>
       </c>
       <c r="G62" s="15">
-        <v>2009.72</v>
+        <v>2142.43</v>
       </c>
       <c r="H62" s="16">
-        <v>0.0060301206743</v>
+        <v>0.007104800603</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>13</v>
@@ -3154,25 +3133,25 @@
     </row>
     <row r="63" spans="2:10" ht="15" customHeight="1">
       <c r="B63" s="12" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D63" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F63" s="14">
         <v>47800</v>
       </c>
       <c r="G63" s="15">
-        <v>1931.99</v>
+        <v>1666.21</v>
       </c>
       <c r="H63" s="16">
-        <v>0.0057968935183</v>
+        <v>0.0055255433376</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>13</v>
@@ -3183,25 +3162,25 @@
     </row>
     <row r="64" spans="2:10" ht="15" customHeight="1">
       <c r="B64" s="12" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D64" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F64" s="14">
-        <v>20600</v>
+        <v>11171</v>
       </c>
       <c r="G64" s="15">
-        <v>1703.07</v>
+        <v>1666.16</v>
       </c>
       <c r="H64" s="16">
-        <v>0.0051100240913</v>
+        <v>0.0055253775258</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>13</v>
@@ -3212,25 +3191,25 @@
     </row>
     <row r="65" spans="2:10" ht="15" customHeight="1">
       <c r="B65" s="12" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C65" s="13" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D65" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>167</v>
+        <v>36</v>
       </c>
       <c r="F65" s="14">
-        <v>22200</v>
+        <v>13363</v>
       </c>
       <c r="G65" s="15">
-        <v>1588.95</v>
+        <v>1658.53</v>
       </c>
       <c r="H65" s="16">
-        <v>0.0047676095403</v>
+        <v>0.0055000746555</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>13</v>
@@ -3241,25 +3220,25 @@
     </row>
     <row r="66" spans="2:10" ht="15" customHeight="1">
       <c r="B66" s="12" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C66" s="13" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D66" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F66" s="14">
         <v>49330</v>
       </c>
       <c r="G66" s="15">
-        <v>1532.24</v>
+        <v>1622.56</v>
       </c>
       <c r="H66" s="16">
-        <v>0.0045974524322</v>
+        <v>0.0053807896951</v>
       </c>
       <c r="I66" s="15" t="s">
         <v>13</v>
@@ -3270,25 +3249,25 @@
     </row>
     <row r="67" spans="2:10" ht="15" customHeight="1">
       <c r="B67" s="12" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D67" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>173</v>
+        <v>33</v>
       </c>
       <c r="F67" s="14">
-        <v>34600</v>
+        <v>16946</v>
       </c>
       <c r="G67" s="15">
-        <v>1280.66</v>
+        <v>1201.97</v>
       </c>
       <c r="H67" s="16">
-        <v>0.0038425921734</v>
+        <v>0.0039860145633</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>13</v>
@@ -3299,25 +3278,25 @@
     </row>
     <row r="68" spans="2:10" ht="15" customHeight="1">
       <c r="B68" s="12" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D68" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>176</v>
+        <v>129</v>
       </c>
       <c r="F68" s="14">
-        <v>6470</v>
+        <v>1600</v>
       </c>
       <c r="G68" s="15">
-        <v>1195.81</v>
+        <v>1007.64</v>
       </c>
       <c r="H68" s="16">
-        <v>0.0035880016139</v>
+        <v>0.0033415706835</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>13</v>
@@ -3328,25 +3307,25 @@
     </row>
     <row r="69" spans="2:10" ht="15" customHeight="1">
       <c r="B69" s="12" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E69" s="13" t="s">
-        <v>134</v>
+        <v>173</v>
       </c>
       <c r="F69" s="14">
-        <v>1600</v>
+        <v>19378</v>
       </c>
       <c r="G69" s="15">
-        <v>1024.88</v>
+        <v>1003.94</v>
       </c>
       <c r="H69" s="16">
-        <v>0.003075129907</v>
+        <v>0.0033293006153</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>13</v>
@@ -3357,25 +3336,25 @@
     </row>
     <row r="70" spans="2:10" ht="15" customHeight="1">
       <c r="B70" s="12" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D70" s="13" t="s">
         <v>13</v>
       </c>
       <c r="E70" s="13" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="F70" s="14">
-        <v>6363</v>
+        <v>24868</v>
       </c>
       <c r="G70" s="15">
-        <v>953.36</v>
+        <v>927.85</v>
       </c>
       <c r="H70" s="16">
-        <v>0.0028605357194</v>
+        <v>0.0030769683208</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>13</v>
@@ -3386,562 +3365,562 @@
     </row>
     <row r="71" spans="2:10" ht="15" customHeight="1">
       <c r="B71" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J71" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10" ht="15" customHeight="1">
+      <c r="B72" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J72" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10" ht="15" customHeight="1">
+      <c r="B73" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J73" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10" ht="15" customHeight="1">
+      <c r="B74" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I74" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J74" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10" ht="15" customHeight="1">
+      <c r="B75" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J75" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10" ht="15" customHeight="1">
+      <c r="B76" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10" ht="15" customHeight="1">
+      <c r="B77" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J77" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10" ht="15" customHeight="1">
+      <c r="B78" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J78" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10" ht="15" customHeight="1">
+      <c r="B79" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J79" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10" ht="15" customHeight="1">
+      <c r="B80" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J80" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" ht="15" customHeight="1">
+      <c r="B81" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J81" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" ht="15" customHeight="1">
+      <c r="B82" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J82" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" ht="15" customHeight="1">
+      <c r="B83" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J83" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" ht="15" customHeight="1">
+      <c r="B84" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="D71" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E71" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="F71" s="14">
-        <v>6046</v>
-      </c>
-      <c r="G71" s="15">
-        <v>831.22</v>
-      </c>
-      <c r="H71" s="16">
-        <v>0.0024940573348</v>
-      </c>
-      <c r="I71" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J71" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10" ht="15" customHeight="1">
-      <c r="B72" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J72" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10" ht="15" customHeight="1">
-      <c r="B73" s="7" t="s">
+      <c r="C84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G84" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J84" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" ht="15" customHeight="1">
+      <c r="B85" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J85" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" ht="15" customHeight="1">
+      <c r="B86" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="C73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G73" s="9" t="s">
+      <c r="C86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G86" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J86" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" ht="15" customHeight="1">
+      <c r="B87" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J87" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10" ht="15" customHeight="1">
+      <c r="B88" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="H73" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I73" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J73" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10" ht="15" customHeight="1">
-      <c r="B74" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J74" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10" ht="15" customHeight="1">
-      <c r="B75" s="7" t="s">
+      <c r="C88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G88" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J88" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10" ht="15" customHeight="1">
+      <c r="B89" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J89" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10" ht="15" customHeight="1">
+      <c r="B90" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="C75" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I75" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J75" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10" ht="15" customHeight="1">
-      <c r="B76" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J76" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10" ht="15" customHeight="1">
-      <c r="B77" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E77" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I77" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J77" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10" ht="15" customHeight="1">
-      <c r="B78" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J78" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10" ht="15" customHeight="1">
-      <c r="B79" s="7" t="s">
+      <c r="C90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G90" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H90" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J90" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10" ht="15" customHeight="1">
+      <c r="B91" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J91" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10" ht="15" customHeight="1">
+      <c r="B92" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="C79" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G79" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H79" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I79" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J79" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10" ht="15" customHeight="1">
-      <c r="B80" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J80" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" ht="15" customHeight="1">
-      <c r="B81" s="7" t="s">
+      <c r="C92" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G92" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H92" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J92" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10" ht="15" customHeight="1">
+      <c r="B93" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J93" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10" ht="15" customHeight="1">
+      <c r="B94" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I81" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J81" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" ht="15" customHeight="1">
-      <c r="B82" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J82" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10" ht="15" customHeight="1">
-      <c r="B83" s="7" t="s">
+      <c r="C94" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G94" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H94" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J94" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10" ht="15" customHeight="1">
+      <c r="B95" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J95" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="2:10" ht="15" customHeight="1">
+      <c r="B96" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="C83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E83" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H83" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I83" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J83" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" ht="15" customHeight="1">
-      <c r="B84" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J84" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10" ht="15" customHeight="1">
-      <c r="B85" s="7" t="s">
+      <c r="C96" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G96" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H96" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J96" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" ht="15" customHeight="1">
+      <c r="B97" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J97" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" ht="15" customHeight="1">
+      <c r="B98" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="C85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G85" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H85" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I85" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J85" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" ht="15" customHeight="1">
-      <c r="B86" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J86" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10" ht="15" customHeight="1">
-      <c r="B87" s="7" t="s">
+      <c r="C98" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F98" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G98" s="9">
+        <v>1596.80</v>
+      </c>
+      <c r="H98" s="10">
+        <v>0.0052953634905</v>
+      </c>
+      <c r="I98" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J98" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" ht="15" customHeight="1">
+      <c r="B99" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="J99" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" ht="15" customHeight="1">
+      <c r="B100" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="C87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G87" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H87" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I87" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J87" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10" ht="15" customHeight="1">
-      <c r="B88" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J88" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10" ht="15" customHeight="1">
-      <c r="B89" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E89" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H89" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I89" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J89" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="90" spans="2:10" ht="15" customHeight="1">
-      <c r="B90" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J90" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10" ht="15" customHeight="1">
-      <c r="B91" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E91" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G91" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H91" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I91" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J91" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10" ht="15" customHeight="1">
-      <c r="B92" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J92" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="93" spans="2:10" ht="15" customHeight="1">
-      <c r="B93" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E93" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G93" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H93" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I93" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J93" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="94" spans="2:10" ht="15" customHeight="1">
-      <c r="B94" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J94" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="95" spans="2:10" ht="15" customHeight="1">
-      <c r="B95" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E95" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G95" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H95" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I95" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J95" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="96" spans="2:10" ht="15" customHeight="1">
-      <c r="B96" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J96" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="97" spans="2:10" ht="15" customHeight="1">
-      <c r="B97" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D97" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E97" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F97" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G97" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="H97" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="I97" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J97" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="98" spans="2:10" ht="15" customHeight="1">
-      <c r="B98" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J98" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="99" spans="2:10" ht="15" customHeight="1">
-      <c r="B99" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="D99" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E99" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F99" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G99" s="9">
-        <v>1055.68</v>
-      </c>
-      <c r="H99" s="10">
-        <v>0.0031675446298</v>
-      </c>
-      <c r="I99" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="J99" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="100" spans="2:10" ht="15" customHeight="1">
-      <c r="B100" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="J100" s="11" t="s">
+      <c r="C100" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D100" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="G100" s="18">
+        <v>4397.705976600002</v>
+      </c>
+      <c r="H100" s="19">
+        <v>0.014583824943922684</v>
+      </c>
+      <c r="I100" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="J100" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="101" spans="2:10" ht="15" customHeight="1">
       <c r="B101" s="17" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C101" s="18" t="s">
         <v>13</v>
@@ -3956,10 +3935,10 @@
         <v>13</v>
       </c>
       <c r="G101" s="18">
-        <v>3727.3191261000466</v>
+        <v>301546.8159766</v>
       </c>
       <c r="H101" s="19">
-        <v>0.011183739089094832</v>
+        <v>0.9999999999970223</v>
       </c>
       <c r="I101" s="18" t="s">
         <v>13</v>
@@ -3968,62 +3947,42 @@
         <v>13</v>
       </c>
     </row>
-    <row r="102" spans="2:10" ht="15" customHeight="1">
-      <c r="B102" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="C102" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D102" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="E102" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F102" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G102" s="18">
-        <v>333280.2291261</v>
-      </c>
-      <c r="H102" s="19">
-        <v>0.9999999999973949</v>
-      </c>
-      <c r="I102" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="J102" s="20" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="105" spans="2:9" ht="15" customHeight="1">
-      <c r="B105" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C105" s="21"/>
-      <c r="D105" s="21"/>
-      <c r="E105" s="21"/>
-      <c r="F105" s="21"/>
-      <c r="G105" s="21"/>
-      <c r="H105" s="21"/>
-      <c r="I105" s="21"/>
-    </row>
-    <row r="107" spans="2:8" ht="15" customHeight="1">
-      <c r="B107" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="C107" s="21"/>
-      <c r="D107" s="21"/>
-      <c r="E107" s="21"/>
-      <c r="F107" s="21"/>
-      <c r="G107" s="21"/>
-      <c r="H107" s="21"/>
+    <row r="104" spans="2:9" ht="15" customHeight="1">
+      <c r="B104" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C104" s="21"/>
+      <c r="D104" s="21"/>
+      <c r="E104" s="21"/>
+      <c r="F104" s="21"/>
+      <c r="G104" s="21"/>
+      <c r="H104" s="21"/>
+      <c r="I104" s="21"/>
+    </row>
+    <row r="106" spans="2:8" ht="15" customHeight="1">
+      <c r="B106" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="C106" s="21"/>
+      <c r="D106" s="21"/>
+      <c r="E106" s="21"/>
+      <c r="F106" s="21"/>
+      <c r="G106" s="21"/>
+      <c r="H106" s="21"/>
+    </row>
+    <row r="108" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
+      <c r="B108" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="C108" s="23"/>
+      <c r="D108" s="23"/>
+      <c r="E108" s="23"/>
+      <c r="F108" s="23"/>
+      <c r="G108" s="23"/>
+      <c r="H108" s="23"/>
     </row>
     <row r="109" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B109" s="22" t="s">
-        <v>201</v>
-      </c>
+      <c r="B109" s="23"/>
       <c r="C109" s="23"/>
       <c r="D109" s="23"/>
       <c r="E109" s="23"/>
@@ -4067,18 +4026,20 @@
       <c r="G113" s="23"/>
       <c r="H113" s="23"/>
     </row>
-    <row r="114" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B114" s="23"/>
-      <c r="C114" s="23"/>
-      <c r="D114" s="23"/>
-      <c r="E114" s="23"/>
-      <c r="F114" s="23"/>
-      <c r="G114" s="23"/>
-      <c r="H114" s="23"/>
-    </row>
-    <row r="116" spans="2:8" ht="15" customHeight="1">
-      <c r="B116" s="13" t="s">
-        <v>202</v>
+    <row r="115" spans="2:8" ht="15" customHeight="1">
+      <c r="B115" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="C115" s="21"/>
+      <c r="D115" s="21"/>
+      <c r="E115" s="21"/>
+      <c r="F115" s="21"/>
+      <c r="G115" s="21"/>
+      <c r="H115" s="21"/>
+    </row>
+    <row r="116" spans="2:8" ht="27.6" customHeight="1">
+      <c r="B116" s="24" t="s">
+        <v>196</v>
       </c>
       <c r="C116" s="21"/>
       <c r="D116" s="21"/>
@@ -4089,7 +4050,7 @@
     </row>
     <row r="117" spans="2:8" ht="27.6" customHeight="1">
       <c r="B117" s="24" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C117" s="21"/>
       <c r="D117" s="21"/>
@@ -4100,7 +4061,7 @@
     </row>
     <row r="118" spans="2:8" ht="27.6" customHeight="1">
       <c r="B118" s="24" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C118" s="21"/>
       <c r="D118" s="21"/>
@@ -4109,44 +4070,33 @@
       <c r="G118" s="21"/>
       <c r="H118" s="21"/>
     </row>
-    <row r="119" spans="2:8" ht="27.6" customHeight="1">
-      <c r="B119" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="C119" s="21"/>
-      <c r="D119" s="21"/>
-      <c r="E119" s="21"/>
-      <c r="F119" s="21"/>
-      <c r="G119" s="21"/>
-      <c r="H119" s="21"/>
-    </row>
-    <row r="122" ht="15">
-      <c r="B122" s="21" t="s">
-        <v>206</v>
+    <row r="121" ht="15">
+      <c r="B121" s="21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="136" ht="15">
+      <c r="B136" s="21" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="137" ht="15">
       <c r="B137" s="21" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="138" ht="15">
-      <c r="B138" s="21" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B109:H114"/>
+    <mergeCell ref="B108:H113"/>
+    <mergeCell ref="B115:H115"/>
     <mergeCell ref="B116:H116"/>
     <mergeCell ref="B117:H117"/>
     <mergeCell ref="B118:H118"/>
-    <mergeCell ref="B119:H119"/>
     <mergeCell ref="B1:J1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="B105:I105"/>
-    <mergeCell ref="B107:H107"/>
+    <mergeCell ref="B104:I104"/>
+    <mergeCell ref="B106:H106"/>
   </mergeCells>
   <printOptions gridLines="1" headings="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
